--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/COLORADO_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/COLORADO_2010.xlsx
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C134">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C193">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C226">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C693">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C759">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1044">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1156">
